--- a/studentdb4.xlsx
+++ b/studentdb4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YF\YF4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310A9869-B747-48D0-8CD5-57E3DA3DBA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E102EA8-33D9-4906-B979-9FD5AF42129B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="293">
   <si>
     <t>ADM NO</t>
   </si>
@@ -1283,6 +1283,9 @@
       <c r="E2" t="s">
         <v>8</v>
       </c>
+      <c r="F2" t="s">
+        <v>288</v>
+      </c>
       <c r="G2">
         <v>4000</v>
       </c>
@@ -7466,6 +7469,9 @@
       </c>
       <c r="E271" t="s">
         <v>14</v>
+      </c>
+      <c r="F271" t="s">
+        <v>290</v>
       </c>
       <c r="G271">
         <v>4269</v>
